--- a/jogos_2024-12-11.xlsx
+++ b/jogos_2024-12-11.xlsx
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Fola Esch</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
         <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>2.37</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.09</v>
+        <v>2.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.65</v>
+        <v>2.01</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['18', '52', '63', '79']</t>
+          <t>['62', '68', '78', '84']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['66', '70', '73']</t>
+          <t>['6', '12']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45637.66666666666</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.37</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['18', '52', '63', '79']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['66', '70', '73']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45637.66666666666</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fola Esch</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,28 +2217,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="T14" t="n">
         <v>2.37</v>
@@ -2247,53 +2247,53 @@
         <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.01</v>
+        <v>2.27</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['62', '68', '78', '84']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['6', '12']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45637.66666666666</v>
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
         <v>2.88</v>
       </c>
       <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['48', '90+3']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45637.69791666666</v>
@@ -2578,20 +2578,20 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -2604,19 +2604,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
         <v>2.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
@@ -2637,44 +2637,44 @@
         <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
         <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['53', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '90+3']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" t="n">
         <v>1.67</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['53', '68']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45637.69791666666</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O19" t="n">
         <v>3.5</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.88</v>
-      </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="X19" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD19" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45637.69791666666</v>
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.15</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.13</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.63</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.14</v>
       </c>
-      <c r="X20" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['60', '78']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['53', '75', '85']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.37</v>
+        <v>2.49</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45637.70833333334</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O22" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="R22" t="n">
         <v>1.29</v>
@@ -3273,59 +3273,59 @@
         <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V22" t="n">
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X22" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD22" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['8', '10', '30', '63']</t>
+          <t>['42', '87']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['42', '79']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45637.70833333334</v>
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
+      <c r="U23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.34</v>
       </c>
-      <c r="M23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>9</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="X23" t="n">
         <v>3.4</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4.7</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['53', '75']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['34', '78', '88']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>4.75</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45637.70833333334</v>
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X24" t="n">
-        <v>4.35</v>
+        <v>4.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.01</v>
+        <v>2.33</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
+          <t>['34', '78', '88']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG24" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.49</v>
+        <v>3.65</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45637.70833333334</v>
@@ -3610,16 +3610,16 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -3628,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="M25" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="N25" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['25', '53', '61', '66', '75']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.29</v>
       </c>
-      <c r="S25" t="n">
+      <c r="AJ25" t="n">
         <v>3.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['42', '87']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>4.75</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45637.70833333334</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,55 +3765,55 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.8</v>
+        <v>1.47</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.93</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>4.5</v>
+        <v>1.83</v>
       </c>
       <c r="P26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AB26" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AC26" t="n">
         <v>1.8</v>
@@ -3823,25 +3823,25 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['53', '75']</t>
+          <t>['8', '10', '30', '63']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '79']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.88</v>
+        <v>1.08</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.27</v>
+        <v>3.05</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.63</v>
+        <v>1.29</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.57</v>
+        <v>3.75</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45637.70833333334</v>
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.31</v>
+        <v>3.15</v>
       </c>
       <c r="M27" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>8.800000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="O27" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X27" t="n">
         <v>6</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X27" t="n">
-        <v>7.2</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['25', '53', '61', '66', '75']</t>
+          <t>['60', '78']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['53', '75', '85']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.1</v>
+        <v>1.77</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.1</v>
+        <v>1.37</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45637.70833333334</v>
